--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_AVSWAR-CSTD-A0-02-B-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_AVSWAR-CSTD-A0-02-B-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\02_19pfv3\02.CV内部結合2\02.設計\MET-C_AVSWAR-CSTD-対応_MET19PFV3-222\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\BEV\BEV設計・実装\課題管理一覧\フレーム変更漏れ対応\Alertパラメータ設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB2B20F-832B-4C64-A2B1-FD890D761F4F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CD96F0-EB67-4792-8620-64E4675EE7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14305" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認）" sheetId="16" r:id="rId1"/>
@@ -2764,10 +2764,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>SCS1S90</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>UNKNOWN</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2969,6 +2965,10 @@
     <rPh sb="6" eb="8">
       <t>ハンテイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SCS1S14</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -5203,6 +5203,18 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="27" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5266,6 +5278,45 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5293,31 +5344,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5327,24 +5357,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -5401,25 +5413,13 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 5" xfId="2" xr:uid="{D73ADDF5-F884-43E0-9A7C-00CB3D6C3CC1}"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -5465,16 +5465,6 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -8437,8 +8427,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="40173088" y="6633882"/>
-          <a:ext cx="15413601" cy="9777419"/>
+          <a:off x="36383174" y="6464736"/>
+          <a:ext cx="13994894" cy="9445260"/>
           <a:chOff x="40173088" y="6633882"/>
           <a:chExt cx="15413601" cy="9777419"/>
         </a:xfrm>
@@ -9618,11 +9608,287 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>598774</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>111636</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>375503</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>30446</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21C6373D-81A7-4B88-94FF-C3B2050130D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23981433" y="10483631"/>
+          <a:ext cx="1633945" cy="405949"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>162380</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>101488</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>558180</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>131933</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="線吹き出し 1 (枠付き) 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10940D2B-6E74-44DB-BF17-C9F297D243C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17973389" y="9499206"/>
+          <a:ext cx="2253017" cy="1167102"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 52087"/>
+            <a:gd name="adj2" fmla="val 100142"/>
+            <a:gd name="adj3" fmla="val 99237"/>
+            <a:gd name="adj4" fmla="val 267544"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>仕様の表記が誤っているが</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>BA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>表より以下となる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>〇「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>SCS1S14</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>✖「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>SCS1S90</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="エディタ情報設定"/>
@@ -9651,9 +9917,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9691,9 +9957,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -9726,26 +9992,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -9778,26 +10027,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9973,13 +10205,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B67217F-73C6-4474-923D-65746D362F67}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:AN49"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="40" width="2.25" style="206" customWidth="1"/>
     <col min="41" max="16384" width="9" style="206"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="13.5" customHeight="1">
+    <row r="1" spans="1:40" ht="13.6" customHeight="1">
       <c r="A1" s="203"/>
       <c r="B1" s="204"/>
       <c r="C1" s="204"/>
@@ -10021,7 +10253,7 @@
       <c r="AM1" s="204"/>
       <c r="AN1" s="205"/>
     </row>
-    <row r="2" spans="1:40" ht="13.5" customHeight="1">
+    <row r="2" spans="1:40" ht="13.6" customHeight="1">
       <c r="A2" s="207"/>
       <c r="B2" s="208"/>
       <c r="C2" s="208"/>
@@ -10063,7 +10295,7 @@
       <c r="AM2" s="208"/>
       <c r="AN2" s="209"/>
     </row>
-    <row r="3" spans="1:40" ht="13.5" customHeight="1">
+    <row r="3" spans="1:40" ht="13.6" customHeight="1">
       <c r="A3" s="207"/>
       <c r="B3" s="208"/>
       <c r="C3" s="208"/>
@@ -10105,7 +10337,7 @@
       <c r="AM3" s="208"/>
       <c r="AN3" s="209"/>
     </row>
-    <row r="4" spans="1:40" ht="13.5" customHeight="1">
+    <row r="4" spans="1:40" ht="13.6" customHeight="1">
       <c r="A4" s="207"/>
       <c r="B4" s="208"/>
       <c r="C4" s="208"/>
@@ -10147,7 +10379,7 @@
       <c r="AM4" s="208"/>
       <c r="AN4" s="209"/>
     </row>
-    <row r="5" spans="1:40" ht="13.5" customHeight="1">
+    <row r="5" spans="1:40" ht="13.6" customHeight="1">
       <c r="A5" s="207"/>
       <c r="B5" s="208"/>
       <c r="C5" s="208"/>
@@ -10189,7 +10421,7 @@
       <c r="AM5" s="208"/>
       <c r="AN5" s="209"/>
     </row>
-    <row r="6" spans="1:40" ht="13.5" customHeight="1">
+    <row r="6" spans="1:40" ht="13.6" customHeight="1">
       <c r="A6" s="207"/>
       <c r="B6" s="208"/>
       <c r="C6" s="208"/>
@@ -10231,7 +10463,7 @@
       <c r="AM6" s="208"/>
       <c r="AN6" s="209"/>
     </row>
-    <row r="7" spans="1:40" ht="13.5" customHeight="1">
+    <row r="7" spans="1:40" ht="13.6" customHeight="1">
       <c r="A7" s="207"/>
       <c r="B7" s="208"/>
       <c r="C7" s="208"/>
@@ -10273,7 +10505,7 @@
       <c r="AM7" s="208"/>
       <c r="AN7" s="209"/>
     </row>
-    <row r="8" spans="1:40" ht="13.5" customHeight="1">
+    <row r="8" spans="1:40" ht="13.6" customHeight="1">
       <c r="A8" s="207"/>
       <c r="B8" s="208"/>
       <c r="C8" s="208"/>
@@ -10315,94 +10547,94 @@
       <c r="AM8" s="208"/>
       <c r="AN8" s="209"/>
     </row>
-    <row r="9" spans="1:40" ht="28.5" customHeight="1">
-      <c r="A9" s="248" t="str">
+    <row r="9" spans="1:40" ht="28.55" customHeight="1">
+      <c r="A9" s="252" t="str">
         <f ca="1">MID(CELL("filename",A1), FIND("[",CELL("filename",A1))+1, FIND("]",CELL("filename",A1))-FIND("[",CELL("filename",A1))-6)</f>
-        <v>alert_C_AVSWAR-CSTD-A0-02-A-C0</v>
-      </c>
-      <c r="B9" s="249"/>
-      <c r="C9" s="249"/>
-      <c r="D9" s="249"/>
-      <c r="E9" s="249"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="249"/>
-      <c r="H9" s="249"/>
-      <c r="I9" s="249"/>
-      <c r="J9" s="249"/>
-      <c r="K9" s="249"/>
-      <c r="L9" s="249"/>
-      <c r="M9" s="249"/>
-      <c r="N9" s="249"/>
-      <c r="O9" s="249"/>
-      <c r="P9" s="249"/>
-      <c r="Q9" s="249"/>
-      <c r="R9" s="249"/>
-      <c r="S9" s="249"/>
-      <c r="T9" s="249"/>
-      <c r="U9" s="249"/>
-      <c r="V9" s="249"/>
-      <c r="W9" s="249"/>
-      <c r="X9" s="249"/>
-      <c r="Y9" s="249"/>
-      <c r="Z9" s="249"/>
-      <c r="AA9" s="249"/>
-      <c r="AB9" s="249"/>
-      <c r="AC9" s="249"/>
-      <c r="AD9" s="249"/>
-      <c r="AE9" s="249"/>
-      <c r="AF9" s="249"/>
-      <c r="AG9" s="249"/>
-      <c r="AH9" s="249"/>
-      <c r="AI9" s="249"/>
-      <c r="AJ9" s="249"/>
-      <c r="AK9" s="249"/>
-      <c r="AL9" s="249"/>
-      <c r="AM9" s="249"/>
-      <c r="AN9" s="250"/>
-    </row>
-    <row r="10" spans="1:40" ht="28.5" customHeight="1">
-      <c r="A10" s="248"/>
-      <c r="B10" s="249"/>
-      <c r="C10" s="249"/>
-      <c r="D10" s="249"/>
-      <c r="E10" s="249"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="249"/>
-      <c r="H10" s="249"/>
-      <c r="I10" s="249"/>
-      <c r="J10" s="249"/>
-      <c r="K10" s="249"/>
-      <c r="L10" s="249"/>
-      <c r="M10" s="249"/>
-      <c r="N10" s="249"/>
-      <c r="O10" s="249"/>
-      <c r="P10" s="249"/>
-      <c r="Q10" s="249"/>
-      <c r="R10" s="249"/>
-      <c r="S10" s="249"/>
-      <c r="T10" s="249"/>
-      <c r="U10" s="249"/>
-      <c r="V10" s="249"/>
-      <c r="W10" s="249"/>
-      <c r="X10" s="249"/>
-      <c r="Y10" s="249"/>
-      <c r="Z10" s="249"/>
-      <c r="AA10" s="249"/>
-      <c r="AB10" s="249"/>
-      <c r="AC10" s="249"/>
-      <c r="AD10" s="249"/>
-      <c r="AE10" s="249"/>
-      <c r="AF10" s="249"/>
-      <c r="AG10" s="249"/>
-      <c r="AH10" s="249"/>
-      <c r="AI10" s="249"/>
-      <c r="AJ10" s="249"/>
-      <c r="AK10" s="249"/>
-      <c r="AL10" s="249"/>
-      <c r="AM10" s="249"/>
-      <c r="AN10" s="250"/>
-    </row>
-    <row r="11" spans="1:40" ht="13.5" customHeight="1">
+        <v>alert_C_AVSWAR-CSTD-A0-02-B-C0</v>
+      </c>
+      <c r="B9" s="253"/>
+      <c r="C9" s="253"/>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="253"/>
+      <c r="I9" s="253"/>
+      <c r="J9" s="253"/>
+      <c r="K9" s="253"/>
+      <c r="L9" s="253"/>
+      <c r="M9" s="253"/>
+      <c r="N9" s="253"/>
+      <c r="O9" s="253"/>
+      <c r="P9" s="253"/>
+      <c r="Q9" s="253"/>
+      <c r="R9" s="253"/>
+      <c r="S9" s="253"/>
+      <c r="T9" s="253"/>
+      <c r="U9" s="253"/>
+      <c r="V9" s="253"/>
+      <c r="W9" s="253"/>
+      <c r="X9" s="253"/>
+      <c r="Y9" s="253"/>
+      <c r="Z9" s="253"/>
+      <c r="AA9" s="253"/>
+      <c r="AB9" s="253"/>
+      <c r="AC9" s="253"/>
+      <c r="AD9" s="253"/>
+      <c r="AE9" s="253"/>
+      <c r="AF9" s="253"/>
+      <c r="AG9" s="253"/>
+      <c r="AH9" s="253"/>
+      <c r="AI9" s="253"/>
+      <c r="AJ9" s="253"/>
+      <c r="AK9" s="253"/>
+      <c r="AL9" s="253"/>
+      <c r="AM9" s="253"/>
+      <c r="AN9" s="254"/>
+    </row>
+    <row r="10" spans="1:40" ht="28.55" customHeight="1">
+      <c r="A10" s="252"/>
+      <c r="B10" s="253"/>
+      <c r="C10" s="253"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
+      <c r="F10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="253"/>
+      <c r="I10" s="253"/>
+      <c r="J10" s="253"/>
+      <c r="K10" s="253"/>
+      <c r="L10" s="253"/>
+      <c r="M10" s="253"/>
+      <c r="N10" s="253"/>
+      <c r="O10" s="253"/>
+      <c r="P10" s="253"/>
+      <c r="Q10" s="253"/>
+      <c r="R10" s="253"/>
+      <c r="S10" s="253"/>
+      <c r="T10" s="253"/>
+      <c r="U10" s="253"/>
+      <c r="V10" s="253"/>
+      <c r="W10" s="253"/>
+      <c r="X10" s="253"/>
+      <c r="Y10" s="253"/>
+      <c r="Z10" s="253"/>
+      <c r="AA10" s="253"/>
+      <c r="AB10" s="253"/>
+      <c r="AC10" s="253"/>
+      <c r="AD10" s="253"/>
+      <c r="AE10" s="253"/>
+      <c r="AF10" s="253"/>
+      <c r="AG10" s="253"/>
+      <c r="AH10" s="253"/>
+      <c r="AI10" s="253"/>
+      <c r="AJ10" s="253"/>
+      <c r="AK10" s="253"/>
+      <c r="AL10" s="253"/>
+      <c r="AM10" s="253"/>
+      <c r="AN10" s="254"/>
+    </row>
+    <row r="11" spans="1:40" ht="13.6" customHeight="1">
       <c r="A11" s="207"/>
       <c r="B11" s="208"/>
       <c r="C11" s="208"/>
@@ -10444,7 +10676,7 @@
       <c r="AM11" s="208"/>
       <c r="AN11" s="209"/>
     </row>
-    <row r="12" spans="1:40" ht="13.5" customHeight="1">
+    <row r="12" spans="1:40" ht="13.6" customHeight="1">
       <c r="A12" s="207"/>
       <c r="B12" s="208"/>
       <c r="C12" s="208"/>
@@ -10486,7 +10718,7 @@
       <c r="AM12" s="208"/>
       <c r="AN12" s="209"/>
     </row>
-    <row r="13" spans="1:40" ht="13.5" customHeight="1">
+    <row r="13" spans="1:40" ht="13.6" customHeight="1">
       <c r="A13" s="207"/>
       <c r="B13" s="208"/>
       <c r="C13" s="208"/>
@@ -10528,7 +10760,7 @@
       <c r="AM13" s="208"/>
       <c r="AN13" s="209"/>
     </row>
-    <row r="14" spans="1:40" ht="13.5" customHeight="1">
+    <row r="14" spans="1:40" ht="13.6" customHeight="1">
       <c r="A14" s="207"/>
       <c r="B14" s="208"/>
       <c r="C14" s="208"/>
@@ -10570,7 +10802,7 @@
       <c r="AM14" s="208"/>
       <c r="AN14" s="209"/>
     </row>
-    <row r="15" spans="1:40" ht="13.5" customHeight="1">
+    <row r="15" spans="1:40" ht="13.6" customHeight="1">
       <c r="A15" s="207"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -10612,7 +10844,7 @@
       <c r="AM15" s="208"/>
       <c r="AN15" s="209"/>
     </row>
-    <row r="16" spans="1:40" ht="13.5" customHeight="1">
+    <row r="16" spans="1:40" ht="13.6" customHeight="1">
       <c r="A16" s="207"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -10654,7 +10886,7 @@
       <c r="AM16" s="208"/>
       <c r="AN16" s="209"/>
     </row>
-    <row r="17" spans="1:40" ht="13.5" customHeight="1">
+    <row r="17" spans="1:40" ht="13.6" customHeight="1">
       <c r="A17" s="207"/>
       <c r="B17" s="208"/>
       <c r="C17" s="208"/>
@@ -10696,7 +10928,7 @@
       <c r="AM17" s="208"/>
       <c r="AN17" s="209"/>
     </row>
-    <row r="18" spans="1:40" ht="13.5" customHeight="1">
+    <row r="18" spans="1:40" ht="13.6" customHeight="1">
       <c r="A18" s="207"/>
       <c r="B18" s="208"/>
       <c r="C18" s="208"/>
@@ -10738,7 +10970,7 @@
       <c r="AM18" s="208"/>
       <c r="AN18" s="209"/>
     </row>
-    <row r="19" spans="1:40" ht="13.5" customHeight="1">
+    <row r="19" spans="1:40" ht="13.6" customHeight="1">
       <c r="A19" s="207"/>
       <c r="B19" s="208"/>
       <c r="C19" s="208"/>
@@ -10780,7 +11012,7 @@
       <c r="AM19" s="208"/>
       <c r="AN19" s="209"/>
     </row>
-    <row r="20" spans="1:40" ht="13.5" customHeight="1">
+    <row r="20" spans="1:40" ht="13.6" customHeight="1">
       <c r="A20" s="207"/>
       <c r="B20" s="208"/>
       <c r="C20" s="208"/>
@@ -10822,7 +11054,7 @@
       <c r="AM20" s="208"/>
       <c r="AN20" s="209"/>
     </row>
-    <row r="21" spans="1:40" ht="13.5" customHeight="1">
+    <row r="21" spans="1:40" ht="13.6" customHeight="1">
       <c r="A21" s="207"/>
       <c r="B21" s="208"/>
       <c r="C21" s="208"/>
@@ -10864,7 +11096,7 @@
       <c r="AM21" s="208"/>
       <c r="AN21" s="209"/>
     </row>
-    <row r="22" spans="1:40" ht="13.5" customHeight="1">
+    <row r="22" spans="1:40" ht="13.6" customHeight="1">
       <c r="A22" s="207"/>
       <c r="B22" s="208"/>
       <c r="C22" s="208"/>
@@ -10906,7 +11138,7 @@
       <c r="AM22" s="208"/>
       <c r="AN22" s="209"/>
     </row>
-    <row r="23" spans="1:40" ht="13.5" customHeight="1">
+    <row r="23" spans="1:40" ht="13.6" customHeight="1">
       <c r="A23" s="207"/>
       <c r="B23" s="208"/>
       <c r="C23" s="208"/>
@@ -10948,7 +11180,7 @@
       <c r="AM23" s="208"/>
       <c r="AN23" s="209"/>
     </row>
-    <row r="24" spans="1:40" ht="13.5" customHeight="1">
+    <row r="24" spans="1:40" ht="13.6" customHeight="1">
       <c r="A24" s="207"/>
       <c r="B24" s="208"/>
       <c r="C24" s="208"/>
@@ -10990,7 +11222,7 @@
       <c r="AM24" s="208"/>
       <c r="AN24" s="209"/>
     </row>
-    <row r="25" spans="1:40" ht="13.5" customHeight="1">
+    <row r="25" spans="1:40" ht="13.6" customHeight="1">
       <c r="A25" s="207"/>
       <c r="B25" s="208"/>
       <c r="C25" s="208"/>
@@ -11032,7 +11264,7 @@
       <c r="AM25" s="208"/>
       <c r="AN25" s="209"/>
     </row>
-    <row r="26" spans="1:40" ht="13.5" customHeight="1">
+    <row r="26" spans="1:40" ht="13.6" customHeight="1">
       <c r="A26" s="207"/>
       <c r="B26" s="208"/>
       <c r="C26" s="208"/>
@@ -11076,7 +11308,7 @@
       <c r="AM26" s="208"/>
       <c r="AN26" s="209"/>
     </row>
-    <row r="27" spans="1:40" ht="13.5" customHeight="1">
+    <row r="27" spans="1:40" ht="13.6" customHeight="1">
       <c r="A27" s="207"/>
       <c r="B27" s="208"/>
       <c r="C27" s="208"/>
@@ -11101,30 +11333,30 @@
       <c r="V27" s="208"/>
       <c r="W27" s="208"/>
       <c r="X27" s="208"/>
-      <c r="Y27" s="245" t="s">
+      <c r="Y27" s="249" t="s">
         <v>217</v>
       </c>
-      <c r="Z27" s="246"/>
-      <c r="AA27" s="246"/>
-      <c r="AB27" s="246"/>
-      <c r="AC27" s="247"/>
-      <c r="AD27" s="245" t="s">
+      <c r="Z27" s="250"/>
+      <c r="AA27" s="250"/>
+      <c r="AB27" s="250"/>
+      <c r="AC27" s="251"/>
+      <c r="AD27" s="249" t="s">
         <v>218</v>
       </c>
-      <c r="AE27" s="246"/>
-      <c r="AF27" s="246"/>
-      <c r="AG27" s="246"/>
-      <c r="AH27" s="247"/>
-      <c r="AI27" s="251" t="s">
+      <c r="AE27" s="250"/>
+      <c r="AF27" s="250"/>
+      <c r="AG27" s="250"/>
+      <c r="AH27" s="251"/>
+      <c r="AI27" s="255" t="s">
         <v>219</v>
       </c>
-      <c r="AJ27" s="246"/>
-      <c r="AK27" s="246"/>
-      <c r="AL27" s="246"/>
-      <c r="AM27" s="247"/>
+      <c r="AJ27" s="250"/>
+      <c r="AK27" s="250"/>
+      <c r="AL27" s="250"/>
+      <c r="AM27" s="251"/>
       <c r="AN27" s="209"/>
     </row>
-    <row r="28" spans="1:40" ht="13.5" customHeight="1">
+    <row r="28" spans="1:40" ht="13.6" customHeight="1">
       <c r="A28" s="207"/>
       <c r="B28" s="208"/>
       <c r="C28" s="208"/>
@@ -11166,7 +11398,7 @@
       <c r="AM28" s="205"/>
       <c r="AN28" s="209"/>
     </row>
-    <row r="29" spans="1:40" ht="13.5" customHeight="1">
+    <row r="29" spans="1:40" ht="13.6" customHeight="1">
       <c r="A29" s="207"/>
       <c r="B29" s="208"/>
       <c r="C29" s="208"/>
@@ -11208,7 +11440,7 @@
       <c r="AM29" s="209"/>
       <c r="AN29" s="209"/>
     </row>
-    <row r="30" spans="1:40" ht="13.5" customHeight="1">
+    <row r="30" spans="1:40" ht="13.6" customHeight="1">
       <c r="A30" s="207"/>
       <c r="B30" s="208"/>
       <c r="C30" s="208"/>
@@ -11254,7 +11486,7 @@
       <c r="AM30" s="209"/>
       <c r="AN30" s="209"/>
     </row>
-    <row r="31" spans="1:40" ht="13.5" customHeight="1">
+    <row r="31" spans="1:40" ht="13.6" customHeight="1">
       <c r="A31" s="207"/>
       <c r="B31" s="208"/>
       <c r="C31" s="208"/>
@@ -11296,7 +11528,7 @@
       <c r="AM31" s="209"/>
       <c r="AN31" s="209"/>
     </row>
-    <row r="32" spans="1:40" ht="13.5" customHeight="1">
+    <row r="32" spans="1:40" ht="13.6" customHeight="1">
       <c r="A32" s="207"/>
       <c r="B32" s="208"/>
       <c r="C32" s="208"/>
@@ -11338,7 +11570,7 @@
       <c r="AM32" s="217"/>
       <c r="AN32" s="209"/>
     </row>
-    <row r="33" spans="1:40" ht="13.5" customHeight="1">
+    <row r="33" spans="1:40" ht="13.6" customHeight="1">
       <c r="A33" s="207"/>
       <c r="B33" s="208"/>
       <c r="C33" s="208"/>
@@ -11380,7 +11612,7 @@
       <c r="AM33" s="208"/>
       <c r="AN33" s="209"/>
     </row>
-    <row r="34" spans="1:40" ht="13.5" customHeight="1">
+    <row r="34" spans="1:40" ht="13.6" customHeight="1">
       <c r="A34" s="207"/>
       <c r="B34" s="208"/>
       <c r="C34" s="208"/>
@@ -11424,7 +11656,7 @@
       <c r="AM34" s="208"/>
       <c r="AN34" s="209"/>
     </row>
-    <row r="35" spans="1:40" ht="13.5" customHeight="1">
+    <row r="35" spans="1:40" ht="13.6" customHeight="1">
       <c r="A35" s="207"/>
       <c r="B35" s="208"/>
       <c r="C35" s="208"/>
@@ -11449,30 +11681,30 @@
       <c r="V35" s="208"/>
       <c r="W35" s="208"/>
       <c r="X35" s="208"/>
-      <c r="Y35" s="245" t="s">
+      <c r="Y35" s="249" t="s">
         <v>217</v>
       </c>
-      <c r="Z35" s="246"/>
-      <c r="AA35" s="246"/>
-      <c r="AB35" s="246"/>
-      <c r="AC35" s="247"/>
-      <c r="AD35" s="245" t="s">
+      <c r="Z35" s="250"/>
+      <c r="AA35" s="250"/>
+      <c r="AB35" s="250"/>
+      <c r="AC35" s="251"/>
+      <c r="AD35" s="249" t="s">
         <v>218</v>
       </c>
-      <c r="AE35" s="246"/>
-      <c r="AF35" s="246"/>
-      <c r="AG35" s="246"/>
-      <c r="AH35" s="247"/>
-      <c r="AI35" s="251" t="s">
+      <c r="AE35" s="250"/>
+      <c r="AF35" s="250"/>
+      <c r="AG35" s="250"/>
+      <c r="AH35" s="251"/>
+      <c r="AI35" s="255" t="s">
         <v>219</v>
       </c>
-      <c r="AJ35" s="246"/>
-      <c r="AK35" s="246"/>
-      <c r="AL35" s="246"/>
-      <c r="AM35" s="247"/>
+      <c r="AJ35" s="250"/>
+      <c r="AK35" s="250"/>
+      <c r="AL35" s="250"/>
+      <c r="AM35" s="251"/>
       <c r="AN35" s="209"/>
     </row>
-    <row r="36" spans="1:40" ht="13.5" customHeight="1">
+    <row r="36" spans="1:40" ht="13.6" customHeight="1">
       <c r="A36" s="207"/>
       <c r="B36" s="208"/>
       <c r="C36" s="208"/>
@@ -11514,7 +11746,7 @@
       <c r="AM36" s="205"/>
       <c r="AN36" s="209"/>
     </row>
-    <row r="37" spans="1:40" ht="13.5" customHeight="1">
+    <row r="37" spans="1:40" ht="13.6" customHeight="1">
       <c r="A37" s="207"/>
       <c r="B37" s="208"/>
       <c r="C37" s="208"/>
@@ -11556,7 +11788,7 @@
       <c r="AM37" s="209"/>
       <c r="AN37" s="209"/>
     </row>
-    <row r="38" spans="1:40" ht="13.5" customHeight="1">
+    <row r="38" spans="1:40" ht="13.6" customHeight="1">
       <c r="A38" s="207"/>
       <c r="B38" s="208"/>
       <c r="C38" s="208"/>
@@ -11604,7 +11836,7 @@
       <c r="AM38" s="209"/>
       <c r="AN38" s="209"/>
     </row>
-    <row r="39" spans="1:40" ht="13.5" customHeight="1">
+    <row r="39" spans="1:40" ht="13.6" customHeight="1">
       <c r="A39" s="207"/>
       <c r="B39" s="208"/>
       <c r="C39" s="208"/>
@@ -11646,7 +11878,7 @@
       <c r="AM39" s="209"/>
       <c r="AN39" s="209"/>
     </row>
-    <row r="40" spans="1:40" ht="13.5" customHeight="1">
+    <row r="40" spans="1:40" ht="13.6" customHeight="1">
       <c r="A40" s="207"/>
       <c r="B40" s="208"/>
       <c r="C40" s="208"/>
@@ -11688,7 +11920,7 @@
       <c r="AM40" s="216"/>
       <c r="AN40" s="209"/>
     </row>
-    <row r="41" spans="1:40" ht="13.5" customHeight="1">
+    <row r="41" spans="1:40" ht="13.6" customHeight="1">
       <c r="A41" s="207"/>
       <c r="B41" s="208"/>
       <c r="C41" s="208"/>
@@ -11730,7 +11962,7 @@
       <c r="AM41" s="208"/>
       <c r="AN41" s="209"/>
     </row>
-    <row r="42" spans="1:40" ht="13.5" customHeight="1">
+    <row r="42" spans="1:40" ht="13.6" customHeight="1">
       <c r="A42" s="207"/>
       <c r="B42" s="208"/>
       <c r="C42" s="208"/>
@@ -11774,7 +12006,7 @@
       <c r="AM42" s="208"/>
       <c r="AN42" s="209"/>
     </row>
-    <row r="43" spans="1:40" ht="13.5" customHeight="1">
+    <row r="43" spans="1:40" ht="13.6" customHeight="1">
       <c r="A43" s="207"/>
       <c r="B43" s="208"/>
       <c r="C43" s="208"/>
@@ -11799,30 +12031,30 @@
       <c r="V43" s="208"/>
       <c r="W43" s="208"/>
       <c r="X43" s="208"/>
-      <c r="Y43" s="245" t="s">
+      <c r="Y43" s="249" t="s">
         <v>217</v>
       </c>
-      <c r="Z43" s="246"/>
-      <c r="AA43" s="246"/>
-      <c r="AB43" s="246"/>
-      <c r="AC43" s="247"/>
-      <c r="AD43" s="245" t="s">
+      <c r="Z43" s="250"/>
+      <c r="AA43" s="250"/>
+      <c r="AB43" s="250"/>
+      <c r="AC43" s="251"/>
+      <c r="AD43" s="249" t="s">
         <v>218</v>
       </c>
-      <c r="AE43" s="246"/>
-      <c r="AF43" s="246"/>
-      <c r="AG43" s="246"/>
-      <c r="AH43" s="247"/>
-      <c r="AI43" s="245" t="s">
+      <c r="AE43" s="250"/>
+      <c r="AF43" s="250"/>
+      <c r="AG43" s="250"/>
+      <c r="AH43" s="251"/>
+      <c r="AI43" s="249" t="s">
         <v>219</v>
       </c>
-      <c r="AJ43" s="246"/>
-      <c r="AK43" s="246"/>
-      <c r="AL43" s="246"/>
-      <c r="AM43" s="247"/>
+      <c r="AJ43" s="250"/>
+      <c r="AK43" s="250"/>
+      <c r="AL43" s="250"/>
+      <c r="AM43" s="251"/>
       <c r="AN43" s="209"/>
     </row>
-    <row r="44" spans="1:40" ht="13.5" customHeight="1">
+    <row r="44" spans="1:40" ht="13.6" customHeight="1">
       <c r="A44" s="207"/>
       <c r="B44" s="208"/>
       <c r="C44" s="208"/>
@@ -11864,7 +12096,7 @@
       <c r="AM44" s="205"/>
       <c r="AN44" s="209"/>
     </row>
-    <row r="45" spans="1:40" ht="13.5" customHeight="1">
+    <row r="45" spans="1:40" ht="13.6" customHeight="1">
       <c r="A45" s="207"/>
       <c r="B45" s="208"/>
       <c r="C45" s="208"/>
@@ -11906,7 +12138,7 @@
       <c r="AM45" s="209"/>
       <c r="AN45" s="209"/>
     </row>
-    <row r="46" spans="1:40" ht="13.5" customHeight="1">
+    <row r="46" spans="1:40" ht="13.6" customHeight="1">
       <c r="A46" s="207"/>
       <c r="B46" s="208"/>
       <c r="C46" s="208"/>
@@ -11948,7 +12180,7 @@
       <c r="AM46" s="209"/>
       <c r="AN46" s="209"/>
     </row>
-    <row r="47" spans="1:40" ht="13.5" customHeight="1">
+    <row r="47" spans="1:40" ht="13.6" customHeight="1">
       <c r="A47" s="207"/>
       <c r="B47" s="208"/>
       <c r="C47" s="208"/>
@@ -11990,7 +12222,7 @@
       <c r="AM47" s="209"/>
       <c r="AN47" s="209"/>
     </row>
-    <row r="48" spans="1:40" ht="13.5" customHeight="1">
+    <row r="48" spans="1:40" ht="13.6" customHeight="1">
       <c r="A48" s="207"/>
       <c r="B48" s="208"/>
       <c r="C48" s="208"/>
@@ -12032,7 +12264,7 @@
       <c r="AM48" s="217"/>
       <c r="AN48" s="209"/>
     </row>
-    <row r="49" spans="1:40" ht="13.5" customHeight="1">
+    <row r="49" spans="1:40" ht="13.6" customHeight="1">
       <c r="A49" s="214"/>
       <c r="B49" s="215"/>
       <c r="C49" s="215"/>
@@ -12091,6 +12323,9 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="89" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -12098,7 +12333,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="10" hidden="1" customWidth="1"/>
@@ -12116,42 +12351,42 @@
       <c r="H2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="252" t="s">
+      <c r="I2" s="256" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
-      <c r="M2" s="252"/>
-      <c r="N2" s="252"/>
-      <c r="O2" s="252"/>
-      <c r="P2" s="252"/>
-      <c r="Q2" s="252"/>
-      <c r="R2" s="252"/>
+      <c r="J2" s="256"/>
+      <c r="K2" s="256"/>
+      <c r="L2" s="256"/>
+      <c r="M2" s="256"/>
+      <c r="N2" s="256"/>
+      <c r="O2" s="256"/>
+      <c r="P2" s="256"/>
+      <c r="Q2" s="256"/>
+      <c r="R2" s="256"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="7"/>
       <c r="D3" s="11" t="str">
         <f ca="1">REPLACE(LEFT(CELL("filename",$B$1),FIND(".xls",CELL("filename",$B$1))-1),1,FIND("[",CELL("filename",$B$1)),)</f>
-        <v>alert_C_AVSWAR-CSTD-A0-02-A-C0</v>
+        <v>alert_C_AVSWAR-CSTD-A0-02-B-C0</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="H3" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="253" t="s">
+      <c r="I3" s="257" t="s">
         <v>175</v>
       </c>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="M3" s="254"/>
-      <c r="N3" s="254"/>
-      <c r="O3" s="254"/>
-      <c r="P3" s="254"/>
-      <c r="Q3" s="254"/>
-      <c r="R3" s="254"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
+      <c r="M3" s="258"/>
+      <c r="N3" s="258"/>
+      <c r="O3" s="258"/>
+      <c r="P3" s="258"/>
+      <c r="Q3" s="258"/>
+      <c r="R3" s="258"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="7"/>
@@ -12175,42 +12410,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
+    <row r="6" spans="2:24" ht="13.6" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="258" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="259"/>
-      <c r="E7" s="260" t="s">
+      <c r="C7" s="262" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="263"/>
+      <c r="E7" s="264" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="260"/>
-      <c r="G7" s="261" t="s">
+      <c r="F7" s="264"/>
+      <c r="G7" s="265" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="261"/>
-      <c r="I7" s="261"/>
-      <c r="J7" s="261"/>
-      <c r="K7" s="261"/>
-      <c r="L7" s="261"/>
-      <c r="M7" s="262" t="s">
+      <c r="H7" s="265"/>
+      <c r="I7" s="265"/>
+      <c r="J7" s="265"/>
+      <c r="K7" s="265"/>
+      <c r="L7" s="265"/>
+      <c r="M7" s="266" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="262"/>
-      <c r="O7" s="262"/>
-      <c r="P7" s="262"/>
-      <c r="Q7" s="262"/>
-      <c r="R7" s="263"/>
-      <c r="S7" s="255" t="s">
+      <c r="N7" s="266"/>
+      <c r="O7" s="266"/>
+      <c r="P7" s="266"/>
+      <c r="Q7" s="266"/>
+      <c r="R7" s="267"/>
+      <c r="S7" s="259" t="s">
         <v>226</v>
       </c>
-      <c r="T7" s="256"/>
-      <c r="U7" s="256"/>
-      <c r="V7" s="256"/>
-      <c r="W7" s="256"/>
-      <c r="X7" s="257"/>
-    </row>
-    <row r="8" spans="2:24" ht="27.75" thickBot="1">
+      <c r="T7" s="260"/>
+      <c r="U7" s="260"/>
+      <c r="V7" s="260"/>
+      <c r="W7" s="260"/>
+      <c r="X7" s="261"/>
+    </row>
+    <row r="8" spans="2:24" ht="26.5" thickBot="1">
       <c r="B8" s="10" t="s">
         <v>91</v>
       </c>
@@ -12281,7 +12516,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="14.25" thickTop="1">
+    <row r="9" spans="2:24" ht="13.6" thickTop="1">
       <c r="B9" s="10">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -12437,7 +12672,7 @@
       <c r="W12" s="14"/>
       <c r="X12" s="191"/>
     </row>
-    <row r="13" spans="2:24" ht="14.25" thickBot="1">
+    <row r="13" spans="2:24" ht="13.6" thickBot="1">
       <c r="B13" s="10">
         <f>IF(C13=0,0,ROW()-ROW($B$8))</f>
         <v>0</v>
@@ -12481,6 +12716,9 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -12488,7 +12726,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="4.625" customWidth="1"/>
     <col min="3" max="3" width="3.5" customWidth="1"/>
@@ -12506,13 +12744,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.25" thickBot="1">
+    <row r="6" spans="2:5" ht="13.6" thickBot="1">
       <c r="B6" s="145" t="s">
         <v>126</v>
       </c>
       <c r="C6" s="145"/>
     </row>
-    <row r="7" spans="2:5" ht="14.25" thickBot="1">
+    <row r="7" spans="2:5" ht="13.6" thickBot="1">
       <c r="C7" s="75" t="s">
         <v>128</v>
       </c>
@@ -12537,7 +12775,7 @@
       <c r="D9" s="157"/>
       <c r="E9" s="156"/>
     </row>
-    <row r="10" spans="2:5" ht="14.25" thickBot="1">
+    <row r="10" spans="2:5" ht="13.6" thickBot="1">
       <c r="C10" s="153"/>
       <c r="D10" s="86"/>
       <c r="E10" s="6"/>
@@ -12545,14 +12783,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="151"/>
     </row>
-    <row r="12" spans="2:5" ht="14.25" thickBot="1">
+    <row r="12" spans="2:5" ht="13.6" thickBot="1">
       <c r="B12" s="146" t="s">
         <v>127</v>
       </c>
       <c r="C12" s="82"/>
       <c r="D12" s="82"/>
     </row>
-    <row r="13" spans="2:5" ht="14.25" thickBot="1">
+    <row r="13" spans="2:5" ht="13.6" thickBot="1">
       <c r="B13" s="147"/>
       <c r="C13" s="152" t="s">
         <v>128</v>
@@ -12564,7 +12802,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="14.25" thickTop="1">
+    <row r="14" spans="2:5" ht="13.6" thickTop="1">
       <c r="C14" s="149">
         <v>0</v>
       </c>
@@ -12641,17 +12879,17 @@
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="14.25" thickBot="1">
+    <row r="21" spans="2:5" ht="13.6" thickBot="1">
       <c r="C21" s="153"/>
       <c r="D21" s="86"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="24" spans="2:5" ht="14.25" thickBot="1">
+    <row r="24" spans="2:5" ht="13.6" thickBot="1">
       <c r="B24" s="145" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="14.25" thickBot="1">
+    <row r="25" spans="2:5" ht="13.6" thickBot="1">
       <c r="C25" s="152" t="s">
         <v>128</v>
       </c>
@@ -12673,7 +12911,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="120" customHeight="1">
+    <row r="27" spans="2:5" ht="120.1" customHeight="1">
       <c r="C27" s="150">
         <v>1</v>
       </c>
@@ -12738,26 +12976,26 @@
       <c r="D33" s="85"/>
       <c r="E33" s="71"/>
     </row>
-    <row r="34" spans="2:5" ht="14.25" thickBot="1">
+    <row r="34" spans="2:5" ht="13.6" thickBot="1">
       <c r="C34" s="153"/>
       <c r="D34" s="86"/>
       <c r="E34" s="6"/>
     </row>
-    <row r="37" spans="2:5" ht="14.25" thickBot="1">
+    <row r="37" spans="2:5" ht="13.6" thickBot="1">
       <c r="B37" s="145" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="264"/>
-      <c r="D38" s="265"/>
+      <c r="C38" s="268"/>
+      <c r="D38" s="269"/>
       <c r="E38" s="110" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="266"/>
-      <c r="D39" s="267"/>
+    <row r="39" spans="2:5" ht="13.6" thickBot="1">
+      <c r="C39" s="270"/>
+      <c r="D39" s="271"/>
       <c r="E39" s="6" t="s">
         <v>118</v>
       </c>
@@ -12773,6 +13011,9 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -12782,7 +13023,7 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
@@ -12792,123 +13033,123 @@
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.6" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="280" t="s">
+      <c r="B2" s="294" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="281"/>
-      <c r="D2" s="268" t="s">
+      <c r="C2" s="295"/>
+      <c r="D2" s="285" t="s">
         <v>235</v>
       </c>
-      <c r="E2" s="269"/>
-      <c r="F2" s="269"/>
-      <c r="G2" s="269"/>
-      <c r="H2" s="270"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="287"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="282" t="s">
+      <c r="B3" s="272" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="283"/>
-      <c r="D3" s="286" t="s">
+      <c r="C3" s="273"/>
+      <c r="D3" s="296" t="s">
         <v>236</v>
       </c>
-      <c r="E3" s="287"/>
-      <c r="F3" s="287"/>
-      <c r="G3" s="287"/>
-      <c r="H3" s="288"/>
-    </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="284" t="s">
+      <c r="E3" s="297"/>
+      <c r="F3" s="297"/>
+      <c r="G3" s="297"/>
+      <c r="H3" s="298"/>
+    </row>
+    <row r="4" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B4" s="283" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="285"/>
-      <c r="D4" s="271" t="str">
+      <c r="C4" s="284"/>
+      <c r="D4" s="288" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
-        <v>alert_C_AVSWAR-CSTD-A0-02-A-C0.c</v>
-      </c>
-      <c r="E4" s="272"/>
-      <c r="F4" s="272"/>
-      <c r="G4" s="272"/>
-      <c r="H4" s="273"/>
-    </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1">
+        <v>alert_C_AVSWAR-CSTD-A0-02-B-C0.c</v>
+      </c>
+      <c r="E4" s="289"/>
+      <c r="F4" s="289"/>
+      <c r="G4" s="289"/>
+      <c r="H4" s="290"/>
+    </row>
+    <row r="5" spans="2:14" ht="13.6" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="280" t="s">
+      <c r="B6" s="294" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="281"/>
-      <c r="D6" s="274" t="str">
+      <c r="C6" s="295"/>
+      <c r="D6" s="291" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>C_AVSWAR</v>
       </c>
-      <c r="E6" s="275"/>
-      <c r="F6" s="275"/>
-      <c r="G6" s="275"/>
-      <c r="H6" s="276"/>
+      <c r="E6" s="292"/>
+      <c r="F6" s="292"/>
+      <c r="G6" s="292"/>
+      <c r="H6" s="293"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="282" t="s">
+      <c r="B7" s="272" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="283"/>
-      <c r="D7" s="277">
+      <c r="C7" s="273"/>
+      <c r="D7" s="274">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="278"/>
-      <c r="F7" s="278"/>
-      <c r="G7" s="278"/>
-      <c r="H7" s="279"/>
+      <c r="E7" s="275"/>
+      <c r="F7" s="275"/>
+      <c r="G7" s="275"/>
+      <c r="H7" s="276"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="282" t="s">
+      <c r="B8" s="272" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="283"/>
-      <c r="D8" s="277" t="str">
+      <c r="C8" s="273"/>
+      <c r="D8" s="274" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_C_AVSWAR_MTRX</v>
       </c>
-      <c r="E8" s="278"/>
-      <c r="F8" s="278"/>
-      <c r="G8" s="278"/>
-      <c r="H8" s="279"/>
+      <c r="E8" s="275"/>
+      <c r="F8" s="275"/>
+      <c r="G8" s="275"/>
+      <c r="H8" s="276"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="282" t="s">
+      <c r="B9" s="272" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="283"/>
-      <c r="D9" s="289" t="s">
+      <c r="C9" s="273"/>
+      <c r="D9" s="277" t="s">
         <v>206</v>
       </c>
-      <c r="E9" s="290"/>
-      <c r="F9" s="290"/>
-      <c r="G9" s="290"/>
-      <c r="H9" s="291"/>
-    </row>
-    <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="284" t="s">
+      <c r="E9" s="278"/>
+      <c r="F9" s="278"/>
+      <c r="G9" s="278"/>
+      <c r="H9" s="279"/>
+    </row>
+    <row r="10" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B10" s="283" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="285"/>
-      <c r="D10" s="292" t="s">
+      <c r="C10" s="284"/>
+      <c r="D10" s="280" t="s">
         <v>200</v>
       </c>
-      <c r="E10" s="293"/>
-      <c r="F10" s="293"/>
-      <c r="G10" s="293"/>
-      <c r="H10" s="294"/>
-    </row>
-    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
-    <row r="12" spans="2:14" ht="14.25" thickBot="1">
+      <c r="E10" s="281"/>
+      <c r="F10" s="281"/>
+      <c r="G10" s="281"/>
+      <c r="H10" s="282"/>
+    </row>
+    <row r="11" spans="2:14" ht="13.6" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.6" thickBot="1">
       <c r="B12" s="136" t="s">
         <v>33</v>
       </c>
@@ -12943,7 +13184,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="14.25" thickTop="1">
+    <row r="13" spans="2:14" ht="13.6" thickTop="1">
       <c r="B13" s="104">
         <v>1</v>
       </c>
@@ -13796,7 +14037,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="14.25" thickBot="1">
+    <row r="37" spans="2:14" ht="13.6" thickBot="1">
       <c r="B37" s="95">
         <v>25</v>
       </c>
@@ -13837,12 +14078,6 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="D6:H6"/>
@@ -13853,21 +14088,27 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="6" priority="3">
-      <formula>14 &lt; LEN($D$6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="NG">
       <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="expression" dxfId="4" priority="3">
+      <formula>14 &lt; LEN($D$6)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -13882,6 +14123,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -13892,7 +14136,7 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
@@ -13906,7 +14150,7 @@
     <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.25" thickBot="1">
+    <row r="2" spans="2:18" ht="13.6" thickBot="1">
       <c r="B2" t="s">
         <v>192</v>
       </c>
@@ -13914,7 +14158,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.25" thickBot="1">
+    <row r="3" spans="2:18" ht="13.6" thickBot="1">
       <c r="B3" s="136" t="s">
         <v>33</v>
       </c>
@@ -13952,7 +14196,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B4" s="168">
         <v>0</v>
       </c>
@@ -13980,7 +14224,7 @@
       </c>
       <c r="R4" s="135"/>
     </row>
-    <row r="5" spans="2:18" ht="122.25" thickTop="1">
+    <row r="5" spans="2:18" ht="116.85" thickTop="1">
       <c r="B5" s="171">
         <v>1</v>
       </c>
@@ -14514,7 +14758,7 @@
       <c r="Q28" s="140"/>
       <c r="R28" s="115"/>
     </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+    <row r="29" spans="2:18" ht="13.6" thickBot="1">
       <c r="B29" s="172">
         <v>25</v>
       </c>
@@ -14536,7 +14780,7 @@
       <c r="Q29" s="138"/>
       <c r="R29" s="117"/>
     </row>
-    <row r="32" spans="2:18" ht="14.25" thickBot="1">
+    <row r="32" spans="2:18" ht="13.6" thickBot="1">
       <c r="B32" t="s">
         <v>193</v>
       </c>
@@ -14544,7 +14788,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="14.25" thickBot="1">
+    <row r="33" spans="2:18" ht="13.6" thickBot="1">
       <c r="B33" s="136" t="s">
         <v>33</v>
       </c>
@@ -14576,7 +14820,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B34" s="168">
         <v>0</v>
       </c>
@@ -14602,7 +14846,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="14.25" thickTop="1">
+    <row r="35" spans="2:18" ht="13.6" thickTop="1">
       <c r="B35" s="171">
         <v>1</v>
       </c>
@@ -15130,7 +15374,7 @@
       <c r="Q58" s="140"/>
       <c r="R58" s="173"/>
     </row>
-    <row r="59" spans="2:18" ht="14.25" thickBot="1">
+    <row r="59" spans="2:18" ht="13.6" thickBot="1">
       <c r="B59" s="172">
         <v>25</v>
       </c>
@@ -15169,6 +15413,9 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -15179,7 +15426,7 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="28.375" customWidth="1"/>
     <col min="3" max="3" width="15.875" customWidth="1"/>
@@ -15196,12 +15443,12 @@
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.25" thickBot="1">
+    <row r="1" spans="2:21" ht="13.6" thickBot="1">
       <c r="C1" s="88" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="14.25" thickBot="1">
+    <row r="2" spans="2:21" ht="13.6" thickBot="1">
       <c r="B2" s="96" t="s">
         <v>57</v>
       </c>
@@ -15245,7 +15492,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14.3" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="26"/>
       <c r="C3" s="48" t="s">
         <v>107</v>
@@ -15266,12 +15513,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="14.25" thickTop="1">
+    <row r="4" spans="2:21" ht="13.6" thickTop="1">
       <c r="B4" s="107" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C4" s="106" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D4" s="118">
         <v>0</v>
@@ -15321,7 +15568,7 @@
         <v>237</v>
       </c>
       <c r="C5" s="106" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D5" s="118">
         <v>1</v>
@@ -15556,7 +15803,7 @@
       </c>
       <c r="U12" s="28"/>
     </row>
-    <row r="13" spans="2:21" ht="14.25" thickBot="1">
+    <row r="13" spans="2:21" ht="13.6" thickBot="1">
       <c r="B13" s="26"/>
       <c r="C13" s="25"/>
       <c r="D13" s="114"/>
@@ -17807,7 +18054,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="14.25" thickBot="1">
+    <row r="103" spans="2:15" ht="13.6" thickBot="1">
       <c r="B103" s="50"/>
       <c r="C103" s="51"/>
       <c r="D103" s="116"/>
@@ -17839,12 +18086,7 @@
     <protectedRange sqref="G6:H7" name="範囲1_1"/>
   </protectedRanges>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="M4:M103">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
-      <formula>32</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
+  <conditionalFormatting sqref="M3:M103">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>32</formula>
     </cfRule>
@@ -17855,6 +18097,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -17883,7 +18128,7 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="6" style="186" customWidth="1"/>
     <col min="2" max="2" width="16.75" style="186" bestFit="1" customWidth="1"/>
@@ -17913,7 +18158,7 @@
       <c r="B2" s="123" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="299" t="s">
+      <c r="C2" s="303" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="55">
@@ -18012,16 +18257,16 @@
       <c r="AI2" s="55">
         <v>0</v>
       </c>
-      <c r="AJ2" s="301" t="s">
+      <c r="AJ2" s="305" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="213" customHeight="1" thickBot="1">
+    <row r="3" spans="1:49" ht="212.95" customHeight="1" thickBot="1">
       <c r="B3" s="196" t="str">
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="300"/>
+      <c r="C3" s="304"/>
       <c r="D3" s="125" t="s">
         <v>60</v>
       </c>
@@ -18103,25 +18348,25 @@
       <c r="AD3" s="126" t="s">
         <v>61</v>
       </c>
-      <c r="AE3" s="303" t="s">
-        <v>248</v>
-      </c>
-      <c r="AF3" s="305"/>
-      <c r="AG3" s="303" t="s">
+      <c r="AE3" s="307" t="s">
+        <v>281</v>
+      </c>
+      <c r="AF3" s="309"/>
+      <c r="AG3" s="307" t="s">
         <v>247</v>
       </c>
-      <c r="AH3" s="304"/>
-      <c r="AI3" s="305"/>
-      <c r="AJ3" s="302"/>
+      <c r="AH3" s="308"/>
+      <c r="AI3" s="309"/>
+      <c r="AJ3" s="306"/>
       <c r="AR3" s="89" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="295" t="s">
+    <row r="4" spans="1:49" ht="13.6" thickBot="1">
+      <c r="A4" s="299" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="296"/>
+      <c r="B4" s="300"/>
       <c r="C4" s="187"/>
       <c r="D4" s="187"/>
       <c r="E4" s="187"/>
@@ -18165,9 +18410,9 @@
       <c r="AV4" s="78"/>
       <c r="AW4" s="79"/>
     </row>
-    <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="297"/>
-      <c r="B5" s="298"/>
+    <row r="5" spans="1:49" ht="13.6" thickBot="1">
+      <c r="A5" s="301"/>
+      <c r="B5" s="302"/>
       <c r="C5" s="188"/>
       <c r="D5" s="188"/>
       <c r="E5" s="188"/>
@@ -18330,7 +18575,7 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL6" s="186" t="str">
         <f t="shared" ref="AL6:AL69" si="0">IF($AJ6="UNKNOWN","    (U1)ALERT_REQ_UNKNOWN","    (U1)"&amp;"ALERT_REQ_"&amp;$AW$17&amp;"_"&amp;IF($AW$6&lt;&gt;$AW$17,$AW$6&amp;"_","")&amp;AJ6)</f>
@@ -18462,7 +18707,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL7" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18595,7 +18840,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="105" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL8" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18728,7 +18973,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL9" s="186" t="str">
         <f t="shared" si="0"/>
@@ -18858,7 +19103,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL10" s="186" t="str">
         <f t="shared" si="0"/>
@@ -18991,7 +19236,7 @@
         <v>1</v>
       </c>
       <c r="AJ11" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL11" s="186" t="str">
         <f t="shared" si="0"/>
@@ -19124,7 +19369,7 @@
         <v>0</v>
       </c>
       <c r="AJ12" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL12" s="186" t="str">
         <f t="shared" si="0"/>
@@ -19254,7 +19499,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL13" s="186" t="str">
         <f t="shared" si="0"/>
@@ -19387,7 +19632,7 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL14" s="186" t="str">
         <f t="shared" si="0"/>
@@ -19520,7 +19765,7 @@
         <v>1</v>
       </c>
       <c r="AJ15" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL15" s="186" t="str">
         <f t="shared" si="0"/>
@@ -19653,7 +19898,7 @@
         <v>0</v>
       </c>
       <c r="AJ16" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL16" s="186" t="str">
         <f t="shared" si="0"/>
@@ -19682,7 +19927,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="14.25" thickBot="1">
+    <row r="17" spans="2:49" ht="13.6" thickBot="1">
       <c r="B17" s="132"/>
       <c r="C17" s="44">
         <f t="shared" si="2"/>
@@ -19785,7 +20030,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL17" s="186" t="str">
         <f t="shared" si="0"/>
@@ -19917,7 +20162,7 @@
         <v>0</v>
       </c>
       <c r="AJ18" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL18" s="186" t="str">
         <f t="shared" si="0"/>
@@ -20039,7 +20284,7 @@
         <v>1</v>
       </c>
       <c r="AJ19" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL19" s="186" t="str">
         <f t="shared" si="0"/>
@@ -20161,7 +20406,7 @@
         <v>0</v>
       </c>
       <c r="AJ20" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL20" s="186" t="str">
         <f t="shared" si="0"/>
@@ -20283,7 +20528,7 @@
         <v>1</v>
       </c>
       <c r="AJ21" s="105" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL21" s="186" t="str">
         <f t="shared" si="0"/>
@@ -20405,7 +20650,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL22" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20527,7 +20772,7 @@
         <v>1</v>
       </c>
       <c r="AJ23" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL23" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20649,7 +20894,7 @@
         <v>0</v>
       </c>
       <c r="AJ24" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL24" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20771,7 +21016,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL25" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20893,7 +21138,7 @@
         <v>0</v>
       </c>
       <c r="AJ26" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL26" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21015,7 +21260,7 @@
         <v>1</v>
       </c>
       <c r="AJ27" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL27" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21137,7 +21382,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL28" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21259,7 +21504,7 @@
         <v>1</v>
       </c>
       <c r="AJ29" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL29" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21381,7 +21626,7 @@
         <v>0</v>
       </c>
       <c r="AJ30" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL30" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21503,7 +21748,7 @@
         <v>1</v>
       </c>
       <c r="AJ31" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL31" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21625,7 +21870,7 @@
         <v>0</v>
       </c>
       <c r="AJ32" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL32" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21747,7 +21992,7 @@
         <v>1</v>
       </c>
       <c r="AJ33" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL33" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21869,7 +22114,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL34" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21991,7 +22236,7 @@
         <v>1</v>
       </c>
       <c r="AJ35" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL35" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22113,7 +22358,7 @@
         <v>0</v>
       </c>
       <c r="AJ36" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL36" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22235,7 +22480,7 @@
         <v>1</v>
       </c>
       <c r="AJ37" s="105" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL37" s="186" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -26094,7 +26339,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="14.25" thickBot="1">
+    <row r="70" spans="1:46" ht="13.6" thickBot="1">
       <c r="A70" s="53" t="s">
         <v>63</v>
       </c>
@@ -46699,6 +46944,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -46719,7 +46967,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:CY117"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="71.875" customWidth="1"/>
     <col min="3" max="10" width="3.375" customWidth="1"/>
@@ -46732,9 +46980,9 @@
     <col min="17" max="17" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="15" thickBot="1">
-      <c r="B2" s="316" t="s">
-        <v>281</v>
+    <row r="2" spans="2:17" ht="15.65" thickBot="1">
+      <c r="B2" s="248" t="s">
+        <v>280</v>
       </c>
       <c r="C2" s="186"/>
       <c r="D2" s="186"/>
@@ -46752,20 +47000,20 @@
       <c r="P2" s="186"/>
       <c r="Q2" s="186"/>
     </row>
-    <row r="3" spans="2:17" ht="15" thickBot="1">
+    <row r="3" spans="2:17" ht="15.65" thickBot="1">
       <c r="B3" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="306" t="s">
+      <c r="C3" s="310" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="307"/>
-      <c r="E3" s="307"/>
-      <c r="F3" s="307"/>
-      <c r="G3" s="307"/>
-      <c r="H3" s="307"/>
-      <c r="I3" s="307"/>
-      <c r="J3" s="308"/>
+      <c r="D3" s="311"/>
+      <c r="E3" s="311"/>
+      <c r="F3" s="311"/>
+      <c r="G3" s="311"/>
+      <c r="H3" s="311"/>
+      <c r="I3" s="311"/>
+      <c r="J3" s="312"/>
       <c r="K3" s="164"/>
       <c r="L3" s="164"/>
       <c r="M3" s="167"/>
@@ -46802,22 +47050,22 @@
       <c r="B5" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="309" t="s">
+      <c r="C5" s="313" t="s">
         <v>170</v>
       </c>
-      <c r="D5" s="310"/>
-      <c r="E5" s="310"/>
-      <c r="F5" s="310"/>
-      <c r="G5" s="310"/>
-      <c r="H5" s="310"/>
-      <c r="I5" s="310"/>
-      <c r="J5" s="311"/>
+      <c r="D5" s="314"/>
+      <c r="E5" s="314"/>
+      <c r="F5" s="314"/>
+      <c r="G5" s="314"/>
+      <c r="H5" s="314"/>
+      <c r="I5" s="314"/>
+      <c r="J5" s="315"/>
       <c r="K5" s="223" t="s">
         <v>230</v>
       </c>
       <c r="L5" s="224"/>
       <c r="M5" s="28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N5" s="73" t="s">
         <v>22</v>
@@ -46832,7 +47080,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="40.5">
+    <row r="6" spans="2:17" ht="38.75">
       <c r="B6" s="68" t="s">
         <v>32</v>
       </c>
@@ -46873,38 +47121,38 @@
       <c r="O6" s="37"/>
       <c r="P6" s="74"/>
       <c r="Q6" s="87" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="27">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="25.85">
       <c r="B7" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="312" t="s">
+      <c r="C7" s="316" t="s">
         <v>150</v>
       </c>
-      <c r="D7" s="310"/>
-      <c r="E7" s="310"/>
-      <c r="F7" s="310"/>
-      <c r="G7" s="310"/>
-      <c r="H7" s="310"/>
-      <c r="I7" s="310"/>
-      <c r="J7" s="311"/>
+      <c r="D7" s="314"/>
+      <c r="E7" s="314"/>
+      <c r="F7" s="314"/>
+      <c r="G7" s="314"/>
+      <c r="H7" s="314"/>
+      <c r="I7" s="314"/>
+      <c r="J7" s="315"/>
       <c r="K7" s="227" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="L7" s="227" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="M7" s="29"/>
       <c r="N7" s="74"/>
       <c r="O7" s="37"/>
       <c r="P7" s="74"/>
       <c r="Q7" s="71" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="136.5">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="130.44999999999999">
       <c r="B8" s="68" t="s">
         <v>27</v>
       </c>
@@ -46933,7 +47181,7 @@
         <v>160</v>
       </c>
       <c r="K8" s="227" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="L8" s="227" t="s">
         <v>247</v>
@@ -46945,10 +47193,10 @@
       <c r="O8" s="37"/>
       <c r="P8" s="74"/>
       <c r="Q8" s="71" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" ht="154.5" customHeight="1" thickBot="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="154.55000000000001" customHeight="1" thickBot="1">
       <c r="B9" s="70" t="s">
         <v>29</v>
       </c>
@@ -46977,26 +47225,26 @@
         <v>162</v>
       </c>
       <c r="K9" s="228" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L9" s="229" t="s">
+        <v>270</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="N9" s="72"/>
+      <c r="O9" s="246" t="s">
+        <v>267</v>
+      </c>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="245" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="13.6" thickTop="1">
+      <c r="B10" s="240" t="s">
         <v>271</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="N9" s="72"/>
-      <c r="O9" s="314" t="s">
-        <v>268</v>
-      </c>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="313" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" ht="14.25" thickTop="1">
-      <c r="B10" s="240" t="s">
-        <v>272</v>
       </c>
       <c r="C10" s="161" t="s">
         <v>161</v>
@@ -47026,7 +47274,7 @@
         <v>204</v>
       </c>
       <c r="L10" s="231" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M10" s="232" t="s">
         <v>107</v>
@@ -47042,7 +47290,7 @@
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="241" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C11" s="161" t="s">
         <v>161</v>
@@ -47069,26 +47317,26 @@
         <v>161</v>
       </c>
       <c r="K11" s="222" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L11" s="233" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M11" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N11" s="238"/>
       <c r="O11" s="237" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P11" s="238"/>
       <c r="Q11" s="233" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="2:17">
       <c r="B12" s="241" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C12" s="161" t="s">
         <v>161</v>
@@ -47115,17 +47363,17 @@
         <v>161</v>
       </c>
       <c r="K12" s="222" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L12" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M12" s="32" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N12" s="38"/>
       <c r="O12" s="237" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P12" s="38"/>
       <c r="Q12" s="233" t="s">
@@ -47134,7 +47382,7 @@
     </row>
     <row r="13" spans="2:17">
       <c r="B13" s="241" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C13" s="162" t="s">
         <v>161</v>
@@ -47161,10 +47409,10 @@
         <v>161</v>
       </c>
       <c r="K13" s="222" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L13" s="233" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M13" s="32" t="s">
         <v>31</v>
@@ -47180,7 +47428,7 @@
     </row>
     <row r="14" spans="2:17" s="186" customFormat="1">
       <c r="B14" s="241" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C14" s="162" t="s">
         <v>161</v>
@@ -47207,10 +47455,10 @@
         <v>161</v>
       </c>
       <c r="K14" s="243" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L14" s="233" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M14" s="32" t="s">
         <v>31</v>
@@ -47226,7 +47474,7 @@
     </row>
     <row r="15" spans="2:17" s="186" customFormat="1">
       <c r="B15" s="241" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C15" s="162" t="s">
         <v>161</v>
@@ -47256,23 +47504,23 @@
         <v>207</v>
       </c>
       <c r="L15" s="233" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M15" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N15" s="38"/>
       <c r="O15" s="237" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P15" s="38"/>
       <c r="Q15" s="233" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="2:17" s="186" customFormat="1">
       <c r="B16" s="241" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C16" s="162" t="s">
         <v>161</v>
@@ -47302,21 +47550,21 @@
         <v>208</v>
       </c>
       <c r="L16" s="233" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M16" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N16" s="38"/>
       <c r="O16" s="237" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P16" s="38"/>
       <c r="Q16" s="233" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="17" spans="2:61" ht="14.25" thickBot="1">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="17" spans="2:61" ht="13.6" thickBot="1">
       <c r="B17" s="23" t="s">
         <v>234</v>
       </c>
@@ -47358,7 +47606,7 @@
         <v>30</v>
       </c>
       <c r="P17" s="39"/>
-      <c r="Q17" s="315" t="s">
+      <c r="Q17" s="247" t="s">
         <v>30</v>
       </c>
     </row>
@@ -48428,6 +48676,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -48437,7 +48688,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="9" style="186"/>
     <col min="2" max="2" width="4.875" style="186" bestFit="1" customWidth="1"/>
@@ -48446,7 +48697,7 @@
     <col min="5" max="16384" width="9" style="186"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="14.25" thickBot="1">
+    <row r="2" spans="2:4" ht="13.6" thickBot="1">
       <c r="B2" s="81" t="s">
         <v>84</v>
       </c>
@@ -48456,7 +48707,7 @@
       </c>
       <c r="D2" s="82"/>
     </row>
-    <row r="3" spans="2:4" ht="14.25" thickBot="1">
+    <row r="3" spans="2:4" ht="13.6" thickBot="1">
       <c r="B3" s="75" t="s">
         <v>84</v>
       </c>
@@ -48467,7 +48718,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="14.25" thickTop="1">
+    <row r="4" spans="2:4" ht="13.6" thickTop="1">
       <c r="B4" s="13">
         <v>0</v>
       </c>
@@ -48478,7 +48729,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="40.5">
+    <row r="5" spans="2:4" ht="38.75">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -48489,7 +48740,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="27">
+    <row r="6" spans="2:4" ht="25.85">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -48500,7 +48751,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="54">
+    <row r="7" spans="2:4" ht="51.65">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -48511,7 +48762,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="81">
+    <row r="8" spans="2:4" ht="77.45">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -48522,7 +48773,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="41.25" customHeight="1">
+    <row r="9" spans="2:4" ht="41.3" customHeight="1">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -48533,7 +48784,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="27">
+    <row r="10" spans="2:4" ht="25.85">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -48544,7 +48795,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="27">
+    <row r="11" spans="2:4" ht="25.85">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -48555,7 +48806,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="27">
+    <row r="12" spans="2:4" ht="25.85">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -48566,7 +48817,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="27">
+    <row r="13" spans="2:4" ht="25.85">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -48577,7 +48828,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="27">
+    <row r="14" spans="2:4" ht="25.85">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -48588,7 +48839,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="135">
+    <row r="15" spans="2:4" ht="129.1">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -48610,7 +48861,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="27">
+    <row r="17" spans="2:4" ht="25.85">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -48621,7 +48872,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="67.5">
+    <row r="18" spans="2:4" ht="90.35">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -48632,7 +48883,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="40.5">
+    <row r="19" spans="2:4" ht="38.75">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -48643,7 +48894,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="64.5" customHeight="1">
+    <row r="20" spans="2:4" ht="64.55" customHeight="1">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -48665,7 +48916,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="27">
+    <row r="22" spans="2:4" ht="25.85">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -48676,7 +48927,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="27">
+    <row r="23" spans="2:4" ht="25.85">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -48687,7 +48938,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="94.5">
+    <row r="24" spans="2:4" ht="90.35">
       <c r="B24" s="2">
         <v>20</v>
       </c>
@@ -48708,7 +48959,7 @@
       <c r="C26" s="85"/>
       <c r="D26" s="71"/>
     </row>
-    <row r="27" spans="2:4" ht="14.25" thickBot="1">
+    <row r="27" spans="2:4" ht="13.6" thickBot="1">
       <c r="B27" s="4"/>
       <c r="C27" s="86"/>
       <c r="D27" s="6"/>
@@ -48717,5 +48968,8 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>